--- a/AAII_Financials/Yearly/TSBA_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/TSBA_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="92">
   <si>
     <t>TSBA</t>
   </si>
@@ -656,72 +656,75 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>44926</v>
+      </c>
+      <c r="E7" s="2">
         <v>44561</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44196</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>43830</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43465</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43100</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>42735</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42369</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42004</v>
-      </c>
-      <c r="L7" s="2">
-        <v>41639</v>
       </c>
       <c r="M7" s="2">
         <v>41639</v>
       </c>
       <c r="N7" s="2">
+        <v>41639</v>
+      </c>
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40908</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40543</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -753,20 +756,23 @@
         <v>10500</v>
       </c>
       <c r="M8" s="3">
-        <v>9500</v>
+        <v>10500</v>
       </c>
       <c r="N8" s="3">
         <v>9500</v>
       </c>
       <c r="O8" s="3">
+        <v>9500</v>
+      </c>
+      <c r="P8" s="3">
         <v>10100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>9500</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -809,9 +815,12 @@
       <c r="P9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -854,9 +863,12 @@
       <c r="P10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -874,8 +886,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -918,9 +931,12 @@
       <c r="P12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -963,9 +979,12 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1008,9 +1027,12 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1053,9 +1075,12 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1070,8 +1095,9 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1103,20 +1129,23 @@
         <v>1900</v>
       </c>
       <c r="M17" s="3">
-        <v>3100</v>
+        <v>1900</v>
       </c>
       <c r="N17" s="3">
         <v>3100</v>
       </c>
       <c r="O17" s="3">
+        <v>3100</v>
+      </c>
+      <c r="P17" s="3">
         <v>2800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3100</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1148,20 +1177,23 @@
         <v>8600</v>
       </c>
       <c r="M18" s="3">
-        <v>6500</v>
+        <v>8600</v>
       </c>
       <c r="N18" s="3">
         <v>6500</v>
       </c>
       <c r="O18" s="3">
+        <v>6500</v>
+      </c>
+      <c r="P18" s="3">
         <v>7300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>6500</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1179,8 +1211,9 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1212,20 +1245,23 @@
         <v>-6200</v>
       </c>
       <c r="M20" s="3">
-        <v>-4400</v>
+        <v>-6200</v>
       </c>
       <c r="N20" s="3">
         <v>-4400</v>
       </c>
       <c r="O20" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="P20" s="3">
         <v>-5300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-4400</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1244,15 +1280,15 @@
       <c r="H21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I21" s="3">
-        <v>3200</v>
+      <c r="I21" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J21" s="3">
+        <v>3000</v>
+      </c>
+      <c r="K21" s="3">
         <v>3100</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1262,15 +1298,18 @@
       <c r="N21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P21" s="3">
         <v>2400</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1313,9 +1352,12 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1347,20 +1389,23 @@
         <v>2400</v>
       </c>
       <c r="M23" s="3">
-        <v>2100</v>
+        <v>2400</v>
       </c>
       <c r="N23" s="3">
         <v>2100</v>
       </c>
       <c r="O23" s="3">
+        <v>2100</v>
+      </c>
+      <c r="P23" s="3">
         <v>1900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2100</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1392,20 +1437,23 @@
         <v>800</v>
       </c>
       <c r="M24" s="3">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="N24" s="3">
         <v>600</v>
       </c>
       <c r="O24" s="3">
+        <v>600</v>
+      </c>
+      <c r="P24" s="3">
         <v>500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>600</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1448,9 +1496,12 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1482,20 +1533,23 @@
         <v>1700</v>
       </c>
       <c r="M26" s="3">
-        <v>1500</v>
+        <v>1700</v>
       </c>
       <c r="N26" s="3">
         <v>1500</v>
       </c>
       <c r="O26" s="3">
+        <v>1500</v>
+      </c>
+      <c r="P26" s="3">
         <v>1400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1500</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1527,20 +1581,23 @@
         <v>1700</v>
       </c>
       <c r="M27" s="3">
-        <v>1500</v>
+        <v>1700</v>
       </c>
       <c r="N27" s="3">
         <v>1500</v>
       </c>
       <c r="O27" s="3">
+        <v>1500</v>
+      </c>
+      <c r="P27" s="3">
         <v>1400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1500</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1583,9 +1640,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1628,9 +1688,12 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1673,9 +1736,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1718,9 +1784,12 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1752,20 +1821,23 @@
         <v>6200</v>
       </c>
       <c r="M32" s="3">
-        <v>4400</v>
+        <v>6200</v>
       </c>
       <c r="N32" s="3">
         <v>4400</v>
       </c>
       <c r="O32" s="3">
+        <v>4400</v>
+      </c>
+      <c r="P32" s="3">
         <v>5300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>4400</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1797,20 +1869,23 @@
         <v>1700</v>
       </c>
       <c r="M33" s="3">
-        <v>1500</v>
+        <v>1700</v>
       </c>
       <c r="N33" s="3">
         <v>1500</v>
       </c>
       <c r="O33" s="3">
+        <v>1500</v>
+      </c>
+      <c r="P33" s="3">
         <v>1400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1500</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1853,9 +1928,12 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1887,70 +1965,76 @@
         <v>1700</v>
       </c>
       <c r="M35" s="3">
-        <v>1500</v>
+        <v>1700</v>
       </c>
       <c r="N35" s="3">
         <v>1500</v>
       </c>
       <c r="O35" s="3">
+        <v>1500</v>
+      </c>
+      <c r="P35" s="3">
         <v>1400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1500</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>44926</v>
+      </c>
+      <c r="E38" s="2">
         <v>44561</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44196</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>43830</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43465</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43100</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>42735</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42369</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42004</v>
-      </c>
-      <c r="L38" s="2">
-        <v>41639</v>
       </c>
       <c r="M38" s="2">
         <v>41639</v>
       </c>
       <c r="N38" s="2">
+        <v>41639</v>
+      </c>
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40908</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40543</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1968,8 +2052,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1987,8 +2072,9 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -2007,33 +2093,36 @@
       <c r="H41" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I41" s="3">
+      <c r="I41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J41" s="3">
         <v>11900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>9400</v>
-      </c>
-      <c r="K41" s="3">
-        <v>5200</v>
       </c>
       <c r="L41" s="3">
         <v>5200</v>
       </c>
       <c r="M41" s="3">
+        <v>5200</v>
+      </c>
+      <c r="N41" s="3">
         <v>7300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>6900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>6200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5900</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2052,33 +2141,36 @@
       <c r="H42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I42" s="3">
+      <c r="I42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J42" s="3">
         <v>9200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>11300</v>
-      </c>
-      <c r="K42" s="3">
-        <v>8800</v>
       </c>
       <c r="L42" s="3">
         <v>8800</v>
       </c>
       <c r="M42" s="3">
+        <v>8800</v>
+      </c>
+      <c r="N42" s="3">
         <v>8200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>16700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>11500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>10700</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2121,9 +2213,12 @@
       <c r="P43" s="3">
         <v>0</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2166,9 +2261,12 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2211,9 +2309,12 @@
       <c r="P45" s="3">
         <v>0</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3">
+        <v>0</v>
+      </c>
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2256,9 +2357,12 @@
       <c r="P46" s="3">
         <v>0</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3">
+        <v>0</v>
+      </c>
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2301,9 +2405,12 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2322,54 +2429,57 @@
       <c r="H48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I48" s="3">
+      <c r="I48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J48" s="3">
         <v>8300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>8700</v>
-      </c>
-      <c r="K48" s="3">
-        <v>9000</v>
       </c>
       <c r="L48" s="3">
         <v>9000</v>
       </c>
       <c r="M48" s="3">
+        <v>9000</v>
+      </c>
+      <c r="N48" s="3">
         <v>18400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>9300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>7600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>7800</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>600</v>
+      </c>
+      <c r="E49" s="3">
         <v>800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2200</v>
       </c>
-      <c r="I49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J49" s="3" t="s">
         <v>5</v>
       </c>
@@ -2382,8 +2492,8 @@
       <c r="M49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
+      <c r="N49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O49" s="3">
         <v>0</v>
@@ -2391,9 +2501,12 @@
       <c r="P49" s="3">
         <v>0</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2436,9 +2549,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2481,9 +2597,12 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2526,9 +2645,12 @@
       <c r="P52" s="3">
         <v>0</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2571,54 +2693,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>622400</v>
+      </c>
+      <c r="E54" s="3">
         <v>581100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>532700</v>
       </c>
-      <c r="F54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G54" s="3">
+      <c r="G54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H54" s="3">
         <v>426300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>439000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>222800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>218300</v>
-      </c>
-      <c r="K54" s="3">
-        <v>216100</v>
       </c>
       <c r="L54" s="3">
         <v>216100</v>
       </c>
       <c r="M54" s="3">
+        <v>216100</v>
+      </c>
+      <c r="N54" s="3">
         <v>213400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>211900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>205000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>192100</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2636,8 +2764,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2655,8 +2784,9 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2675,8 +2805,8 @@
       <c r="H57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I57" s="3">
-        <v>100</v>
+      <c r="I57" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J57" s="3">
         <v>100</v>
@@ -2691,7 +2821,7 @@
         <v>100</v>
       </c>
       <c r="N57" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O57" s="3">
         <v>200</v>
@@ -2699,9 +2829,12 @@
       <c r="P57" s="3">
         <v>200</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3">
+        <v>200</v>
+      </c>
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2744,9 +2877,12 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2765,33 +2901,36 @@
       <c r="H59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I59" s="3">
+      <c r="I59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J59" s="3">
         <v>1600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1700</v>
-      </c>
-      <c r="K59" s="3">
-        <v>1900</v>
       </c>
       <c r="L59" s="3">
         <v>1900</v>
       </c>
       <c r="M59" s="3">
+        <v>1900</v>
+      </c>
+      <c r="N59" s="3">
         <v>1500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1700</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2834,30 +2973,33 @@
       <c r="P60" s="3">
         <v>0</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3">
+        <v>0</v>
+      </c>
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>48600</v>
+      </c>
+      <c r="E61" s="3">
         <v>7800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>32300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>33500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>8000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>8900</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -2879,9 +3021,12 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2924,9 +3069,12 @@
       <c r="P62" s="3">
         <v>0</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3">
+        <v>0</v>
+      </c>
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2969,9 +3117,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3014,9 +3165,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3059,9 +3213,12 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -3080,33 +3237,36 @@
       <c r="H66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I66" s="3">
+      <c r="I66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J66" s="3">
         <v>197000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>193500</v>
-      </c>
-      <c r="K66" s="3">
-        <v>192500</v>
       </c>
       <c r="L66" s="3">
         <v>192500</v>
       </c>
       <c r="M66" s="3">
+        <v>192500</v>
+      </c>
+      <c r="N66" s="3">
         <v>191200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>190700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>184700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>172600</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3124,8 +3284,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3168,9 +3329,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3213,9 +3377,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3258,9 +3425,12 @@
       <c r="P70" s="3">
         <v>100</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>100</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3303,9 +3473,12 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -3324,33 +3497,36 @@
       <c r="H72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I72" s="3">
+      <c r="I72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J72" s="3">
         <v>16300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>15100</v>
-      </c>
-      <c r="K72" s="3">
-        <v>13900</v>
       </c>
       <c r="L72" s="3">
         <v>13900</v>
       </c>
       <c r="M72" s="3">
+        <v>13900</v>
+      </c>
+      <c r="N72" s="3">
         <v>12600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>11500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>10800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>9900</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3393,9 +3569,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3438,9 +3617,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3483,54 +3665,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>42500</v>
+      </c>
+      <c r="E76" s="3">
         <v>50800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>50000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>47100</v>
       </c>
-      <c r="G76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H76" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I76" s="3">
+      <c r="I76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J76" s="3">
         <v>25700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>24700</v>
-      </c>
-      <c r="K76" s="3">
-        <v>23600</v>
       </c>
       <c r="L76" s="3">
         <v>23600</v>
       </c>
       <c r="M76" s="3">
+        <v>23600</v>
+      </c>
+      <c r="N76" s="3">
         <v>22000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>21100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>20200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>19400</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3573,59 +3761,65 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>44926</v>
+      </c>
+      <c r="E80" s="2">
         <v>44561</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44196</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>43830</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43465</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43100</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>42735</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42369</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42004</v>
-      </c>
-      <c r="L80" s="2">
-        <v>41639</v>
       </c>
       <c r="M80" s="2">
         <v>41639</v>
       </c>
       <c r="N80" s="2">
+        <v>41639</v>
+      </c>
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40908</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40543</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3657,20 +3851,23 @@
         <v>1700</v>
       </c>
       <c r="M81" s="3">
-        <v>1500</v>
+        <v>1700</v>
       </c>
       <c r="N81" s="3">
         <v>1500</v>
       </c>
       <c r="O81" s="3">
+        <v>1500</v>
+      </c>
+      <c r="P81" s="3">
         <v>1400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1500</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3688,8 +3885,9 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3708,14 +3906,14 @@
       <c r="H83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I83" s="3">
-        <v>600</v>
+      <c r="I83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J83" s="3">
         <v>600</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>5</v>
+      <c r="K83" s="3">
+        <v>600</v>
       </c>
       <c r="L83" s="3" t="s">
         <v>5</v>
@@ -3726,15 +3924,18 @@
       <c r="N83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O83" s="3">
+      <c r="O83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P83" s="3">
         <v>500</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3777,9 +3978,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3822,9 +4026,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3867,9 +4074,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3912,9 +4122,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3957,9 +4170,12 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -3978,14 +4194,14 @@
       <c r="H89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I89" s="3">
+      <c r="I89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J89" s="3">
         <v>2000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1900</v>
-      </c>
-      <c r="K89" s="3">
-        <v>3400</v>
       </c>
       <c r="L89" s="3">
         <v>3400</v>
@@ -3994,17 +4210,20 @@
         <v>3400</v>
       </c>
       <c r="N89" s="3">
+        <v>3400</v>
+      </c>
+      <c r="O89" s="3">
         <v>2300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1100</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4022,8 +4241,9 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4042,23 +4262,23 @@
       <c r="H91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I91" s="3">
-        <v>-300</v>
+      <c r="I91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J91" s="3">
         <v>-300</v>
       </c>
       <c r="K91" s="3">
-        <v>-500</v>
+        <v>-300</v>
       </c>
       <c r="L91" s="3">
         <v>-500</v>
       </c>
       <c r="M91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="N91" s="3">
         <v>-2200</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-300</v>
       </c>
       <c r="O91" s="3">
         <v>-300</v>
@@ -4066,9 +4286,12 @@
       <c r="P91" s="3">
         <v>-300</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4111,9 +4334,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4156,9 +4382,12 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4177,15 +4406,15 @@
       <c r="H94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I94" s="3">
+      <c r="I94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J94" s="3">
         <v>-4700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>700</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>5</v>
       </c>
@@ -4195,15 +4424,18 @@
       <c r="N94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O94" s="3">
+      <c r="O94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P94" s="3">
         <v>-11200</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4221,8 +4453,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4242,7 +4475,7 @@
         <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>-500</v>
+        <v>0</v>
       </c>
       <c r="J96" s="3">
         <v>-500</v>
@@ -4254,10 +4487,10 @@
         <v>-500</v>
       </c>
       <c r="M96" s="3">
+        <v>-500</v>
+      </c>
+      <c r="N96" s="3">
         <v>-1000</v>
-      </c>
-      <c r="N96" s="3">
-        <v>-500</v>
       </c>
       <c r="O96" s="3">
         <v>-500</v>
@@ -4265,9 +4498,12 @@
       <c r="P96" s="3">
         <v>-500</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>-500</v>
+      </c>
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4310,9 +4546,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4355,9 +4594,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4400,9 +4642,12 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -4421,15 +4666,15 @@
       <c r="H100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I100" s="3">
+      <c r="I100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J100" s="3">
         <v>3100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>600</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>5</v>
       </c>
@@ -4439,15 +4684,18 @@
       <c r="N100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P100" s="3">
         <v>6800</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4472,8 +4720,8 @@
       <c r="J101" s="3">
         <v>0</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>5</v>
+      <c r="K101" s="3">
+        <v>0</v>
       </c>
       <c r="L101" s="3" t="s">
         <v>5</v>
@@ -4484,15 +4732,18 @@
       <c r="N101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="O101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -4511,31 +4762,34 @@
       <c r="H102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I102" s="3">
+      <c r="I102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J102" s="3">
         <v>400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>3200</v>
-      </c>
-      <c r="K102" s="3">
-        <v>-8100</v>
       </c>
       <c r="L102" s="3">
         <v>-8100</v>
       </c>
       <c r="M102" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="N102" s="3">
         <v>4900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>8700</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
